--- a/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
@@ -5415,7 +5415,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Plano: bastones 2#6 sup. / 1#6 inf. de 100 cm dentro del muro (eje 8) a 120 cm del eje 8. Inf. 1#6 sobre el muro final (de 50 cm del eje 10 al extremo) no capturado. | secciones: T EJE-B Seccion 2 + T EJE-B Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>Plano: bastones 2#6 sup. / 1#6 inf. de 100 cm dentro del muro (eje 8) a 120 cm del eje 8. Inf. 1#6 sobre el muro final hasta el extremo: el botón lo arranca en el paño del muro (en el plano arranca 50 cm pasando el eje 10).</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,11 @@
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="n"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>1#6 0</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="2" t="n"/>
       <c r="P78" s="2" t="inlineStr">

--- a/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
@@ -4564,19 +4564,19 @@
         </is>
       </c>
       <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>2#8 280/60</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>2#8 -100/-130</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>2#8 -100/-130</t>
-        </is>
-      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2#8 280/60</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
           <t>E#3 @10</t>

--- a/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S1]</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Plano: 15X80 con 3#8 y 15X60 con 3#4. Los tramos 4 y 5 (20x80, entre ejes L y K) no vienen detallados: se supuso 3#8 @10. | secciones: T EJE-5 Seccion 1 + T EJE-5 Seccion 2 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>En el plano son vigas separadas: 15X80 ejes N-L (S1, incluye la pieza de 20x80) y 15X60 ejes K-B (S2). | Plano: 15X80 con 3#8 y 15X60 con 3#4. Los tramos 4 y 5 (20x80, entre ejes L y K) no vienen detallados: se supuso 3#8 @10. | secciones: T EJE-5 Seccion 1 + T EJE-5 Seccion 2 (se arman juntas; los bastones pasan el cambio de sección)</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S1]</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S1]</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S1]</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S1]</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2656,20 +2656,20 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S2]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5 (muro bajo la viga)</t>
+          <t>1 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>6 (muro)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2707,7 +2707,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S34" s="2" t="n"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: 15X80 ejes N-L (S1, incluye la pieza de 20x80) y 15X60 ejes K-B (S2).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2717,20 +2721,20 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S2]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>6 (muro)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>7 (muro bajo la viga)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2778,20 +2782,20 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S2]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>7 (muro bajo la viga)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>8 (muro bajo la viga)</t>
+          <t>4 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2847,20 +2851,20 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S2]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>8 (muro bajo la viga)</t>
+          <t>4 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>9 (muro bajo la viga)</t>
+          <t>5 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2908,20 +2912,20 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S2]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>9 (muro bajo la viga)</t>
+          <t>5 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>10 (muro bajo la viga)</t>
+          <t>6 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2969,20 +2973,20 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>EJE-5</t>
+          <t>EJE-5 [S2]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>10 (muro bajo la viga)</t>
+          <t>6 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>11 (muro bajo la viga)</t>
+          <t>7 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -11155,7 +11159,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2)</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -11212,7 +11216,7 @@
       </c>
       <c r="S169" s="2" t="inlineStr">
         <is>
-          <t>Plano: ejes 5-8 (sup. 2#6, inf. 3#6, bastón sup. 3#6 del extremo a 120 cm pasando el muro) y ejes 9-11 (30X80, 3#12). Los tramos 5 y 6 (30x80 antes del eje 9) no vienen detallados: se supuso 3#12 @10. | secciones: T-5 Seccion 1 + T-5 Seccion 2 + T-5 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>En el plano son vigas separadas: ejes 5-8 (S1+S2) y ejes 9-11 (S3, 30X80); cada parte se arma aparte. | Plano: ejes 5-8 (sup. 2#6, inf. 3#6, bastón sup. 3#6 del extremo a 120 cm pasando el muro) y ejes 9-11 (30X80, 3#12). Los tramos 5 y 6 (30x80 antes del eje 9) no vienen detallados: se supuso 3#12 @10. | secciones: T-5 Seccion 1 + T-5 Seccion 2 + T-5 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11228,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2)</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -11285,7 +11289,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2)</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -11346,7 +11350,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2)</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -11407,15 +11411,15 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2)</t>
+          <t>T-5 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
@@ -11458,7 +11462,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S173" s="2" t="n"/>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: ejes 5-8 (S1+S2) y ejes 9-11 (S3, 30X80); cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -11468,11 +11476,11 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2)</t>
+          <t>T-5 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -11481,7 +11489,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -11529,20 +11537,20 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2)</t>
+          <t>T-5 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>7 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -11781,7 +11789,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2)</t>
+          <t>T-6 (viga 2) [S2]</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -11838,7 +11846,7 @@
       </c>
       <c r="S179" s="2" t="inlineStr">
         <is>
-          <t>Los tramos 2 y 3 (30x80 entre ejes 8 y 9) no vienen detallados: se supuso @10. | secciones: T-6 Seccion 2 + T-6 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>En el plano son vigas separadas: 30X80 (S2) y 15X80 (S3); cada parte se arma aparte. | Los tramos 2 y 3 (30x80 entre ejes 8 y 9) no vienen detallados: se supuso @10. | secciones: T-6 Seccion 2 + T-6 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11858,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2)</t>
+          <t>T-6 (viga 2) [S2]</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -11911,7 +11919,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2)</t>
+          <t>T-6 (viga 2) [S2]</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -11972,20 +11980,20 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2)</t>
+          <t>T-6 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -12027,7 +12035,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S182" s="2" t="n"/>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: 30X80 (S2) y 15X80 (S3); cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -12037,20 +12049,20 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2)</t>
+          <t>T-6 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F183" t="n">

--- a/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
@@ -7370,7 +7370,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>EJE-J</t>
+          <t>EJE-J [T1-2]</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -7421,7 +7421,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S108" s="2" t="n"/>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: ejes 3-8 (2#6) y ejes 8-10 (3#4); cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7431,7 +7435,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>EJE-J</t>
+          <t>EJE-J [T1-2]</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -7492,20 +7496,20 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>EJE-J</t>
+          <t>EJE-J [T3]</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -8923,7 +8927,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1)</t>
+          <t>T-2 (viga 1) [T1-2]</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -8976,7 +8980,7 @@
       </c>
       <c r="S133" s="2" t="inlineStr">
         <is>
-          <t>4 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado. | 4 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8992,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1)</t>
+          <t>T-2 (viga 1) [T1-2]</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -9049,20 +9053,20 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1)</t>
+          <t>T-2 (viga 1) [T3]</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -9100,7 +9104,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S135" s="2" t="n"/>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -9110,20 +9118,20 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1)</t>
+          <t>T-2 (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -9161,7 +9169,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S136" s="2" t="n"/>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -9171,20 +9183,20 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1)</t>
+          <t>T-2 (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -9232,7 +9244,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2)</t>
+          <t>T-2 (viga 2) [T1-2]</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -9283,7 +9295,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S138" s="2" t="n"/>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9293,7 +9309,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2)</t>
+          <t>T-2 (viga 2) [T1-2]</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -9354,20 +9370,20 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2)</t>
+          <t>T-2 (viga 2) [T3]</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -9405,7 +9421,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S140" s="2" t="n"/>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9415,20 +9435,20 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2)</t>
+          <t>T-2 (viga 2) [T4-6]</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -9466,7 +9486,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S141" s="2" t="n"/>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9476,20 +9500,20 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2)</t>
+          <t>T-2 (viga 2) [T4-6]</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -9537,20 +9561,20 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2)</t>
+          <t>T-2 (viga 2) [T4-6]</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>7 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -9842,7 +9866,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1)</t>
+          <t>T-2' (viga 1) [T1-2]</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -9895,7 +9919,7 @@
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado. | 2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9931,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1)</t>
+          <t>T-2' (viga 1) [T1-2]</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -9968,20 +9992,20 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1)</t>
+          <t>T-2' (viga 1) [T3]</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -10019,7 +10043,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S150" s="2" t="n"/>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -10029,20 +10057,20 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1)</t>
+          <t>T-2' (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -10080,7 +10108,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S151" s="2" t="n"/>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -10090,20 +10122,20 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1)</t>
+          <t>T-2' (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -11358,7 +11390,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 1)</t>
+          <t>T-6 (viga 1) [T1]</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -11411,7 +11443,7 @@
       </c>
       <c r="S172" s="2" t="inlineStr">
         <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado. | 2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
         </is>
       </c>
     </row>
@@ -11423,20 +11455,20 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 1)</t>
+          <t>T-6 (viga 1) [T2]</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -11474,7 +11506,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S173" s="2" t="n"/>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -11484,20 +11520,20 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 1)</t>
+          <t>T-6 (viga 1) [T3]</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>4 (muro)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -11535,7 +11571,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S174" s="2" t="n"/>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">

--- a/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Roof_Garden_N10.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S241"/>
+  <dimension ref="A1:S236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>EJE-J [T1-2]</t>
+          <t>EJE-J [T1]</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>En el plano son vigas separadas: ejes 3-8 (2#6) y ejes 8-10 (3#4); cada parte se arma aparte.</t>
+          <t>En el plano son vigas separadas: ejes 3-8 (2#6) y ejes 8-10 (3#4). Entre el muro y la viga que cruza no hay trabe en el modelo (hueco del plano).</t>
         </is>
       </c>
     </row>
@@ -7435,24 +7435,24 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>EJE-J [T1-2]</t>
+          <t>EJE-J [T3]</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>2.56</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J109" s="2" t="n"/>
@@ -7477,7 +7477,7 @@
       <c r="O109" s="2" t="n"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q109" s="2" t="n"/>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>EJE-J [T3]</t>
+          <t>EJE-K</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -7504,30 +7504,30 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>1 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2.56</v>
+        <v>1.03</v>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#8</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#8</t>
         </is>
       </c>
       <c r="J110" s="2" t="n"/>
@@ -7538,7 +7538,7 @@
       <c r="O110" s="2" t="n"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q110" s="2" t="n"/>
@@ -7561,20 +7561,20 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>1 (muro bajo la viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1.03</v>
+        <v>4.83</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -7592,14 +7592,22 @@
         </is>
       </c>
       <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>4#8 80/210</t>
+        </is>
+      </c>
       <c r="L111" s="2" t="n"/>
-      <c r="M111" s="2" t="n"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>2#8 80/210</t>
+        </is>
+      </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="2" t="n"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q111" s="2" t="n"/>
@@ -7622,20 +7630,20 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>4 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>4.83</v>
+        <v>1</v>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
@@ -7653,22 +7661,14 @@
         </is>
       </c>
       <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>4#8 80/210</t>
-        </is>
-      </c>
+      <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="n"/>
-      <c r="M112" s="2" t="inlineStr">
-        <is>
-          <t>2#8 80/210</t>
-        </is>
-      </c>
+      <c r="M112" s="2" t="n"/>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="2" t="n"/>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q112" s="2" t="n"/>
@@ -7687,38 +7687,38 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>EJE-K</t>
+          <t>EJE-L (viga 1)</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>4 (muro bajo la viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>1.82</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J113" s="2" t="n"/>
@@ -7729,7 +7729,7 @@
       <c r="O113" s="2" t="n"/>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q113" s="2" t="n"/>
@@ -7738,7 +7738,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S113" s="2" t="n"/>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7752,20 +7756,20 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
@@ -7799,11 +7803,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S114" s="2" t="inlineStr">
-        <is>
-          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7813,24 +7813,24 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>EJE-L (viga 1)</t>
+          <t>EJE-L (viga 2)</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F115" t="n">
-        <v>1.44</v>
+        <v>3.41</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>EJE-L (viga 2)</t>
+          <t>EJE-L (viga 3)</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -7891,21 +7891,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3.41</v>
+        <v>1.4</v>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J116" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       <c r="O116" s="2" t="n"/>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q116" s="2" t="n"/>
@@ -7939,20 +7939,20 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
       <c r="O117" s="2" t="n"/>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q117" s="2" t="n"/>
@@ -7996,38 +7996,38 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>EJE-L (viga 3)</t>
+          <t>EJE-M (viga 1)</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>3 (muro bajo la viga)</t>
-        </is>
-      </c>
       <c r="F118" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J118" s="2" t="n"/>
@@ -8038,7 +8038,7 @@
       <c r="O118" s="2" t="n"/>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q118" s="2" t="n"/>
@@ -8047,7 +8047,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S118" s="2" t="n"/>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8061,20 +8065,20 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (muro)</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -8108,11 +8112,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S119" s="2" t="inlineStr">
-        <is>
-          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8122,24 +8122,24 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>EJE-M (viga 1)</t>
+          <t>EJE-M (viga 2)</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
+          <t>1 (muro)</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>3 (muro)</t>
-        </is>
-      </c>
       <c r="F120" t="n">
-        <v>1.44</v>
+        <v>3.41</v>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>EJE-M (viga 2)</t>
+          <t>EJE-M (viga 3)</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -8191,41 +8191,45 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>1 (muro)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3.41</v>
+        <v>2.56</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J121" s="2" t="n"/>
-      <c r="K121" s="2" t="n"/>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>2#6 80</t>
+        </is>
+      </c>
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n"/>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="2" t="n"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q121" s="2" t="n"/>
@@ -8244,7 +8248,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>EJE-M (viga 3)</t>
+          <t>EJE-N (viga 1)</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -8257,40 +8261,36 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2.56</v>
+        <v>13.56</v>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J122" s="2" t="n"/>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>2#6 80</t>
-        </is>
-      </c>
+      <c r="K122" s="2" t="n"/>
       <c r="L122" s="2" t="n"/>
       <c r="M122" s="2" t="n"/>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="2" t="n"/>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q122" s="2" t="n"/>
@@ -8299,7 +8299,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S122" s="2" t="n"/>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8309,7 +8313,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>EJE-N (viga 1)</t>
+          <t>EJE-N (viga 2)</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -8317,30 +8321,30 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>extremo libre</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>extremo libre</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>13.56</v>
+        <v>7.57</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J123" s="2" t="n"/>
@@ -8360,11 +8364,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S123" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>EJE-N (viga 2)</t>
+          <t>T-0</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -8382,20 +8382,20 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>extremo libre</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>extremo libre</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>7.57</v>
+        <v>3.4</v>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       <c r="O124" s="2" t="n"/>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q124" s="2" t="n"/>
@@ -8439,20 +8439,20 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -8500,16 +8500,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -8561,20 +8561,20 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>5 (viga)</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3.15</v>
+        <v>3.43</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -8618,28 +8618,28 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>T-0</t>
+          <t>T-1 (viga 1)</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3.43</v>
+        <v>1.01</v>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>12x40</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       <c r="O128" s="2" t="n"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q128" s="2" t="n"/>
@@ -8669,7 +8669,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S128" s="2" t="n"/>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8683,20 +8687,20 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -8730,11 +8734,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S129" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8744,24 +8744,24 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>T-1 (viga 1)</t>
+          <t>T-1 (viga 2)</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
           <t>2 (muro bajo la viga)</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F130" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
@@ -8809,20 +8809,20 @@
         </is>
       </c>
       <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>2 (muro bajo la viga)</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
         <v>1</v>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>2 (muro bajo la viga)</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>1.01</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -8866,38 +8866,38 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>T-1 (viga 2)</t>
+          <t>T-2 (viga 1) [T1-2]</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>12x40</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J132" s="2" t="n"/>
@@ -8908,7 +8908,7 @@
       <c r="O132" s="2" t="n"/>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q132" s="2" t="n"/>
@@ -8917,7 +8917,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S132" s="2" t="n"/>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos); entre los dos cajones no hay trabe en el modelo (hueco del plano): cada cajón se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8931,20 +8935,20 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -8969,7 +8973,7 @@
       <c r="O133" s="2" t="n"/>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q133" s="2" t="n"/>
@@ -8978,11 +8982,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S133" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado. | 4 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8992,20 +8992,20 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1) [T1-2]</t>
+          <t>T-2 (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -9034,7 +9034,7 @@
       <c r="O134" s="2" t="n"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q134" s="2" t="n"/>
@@ -9043,7 +9043,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S134" s="2" t="n"/>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -9053,24 +9057,24 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1) [T3]</t>
+          <t>T-2 (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
         <v>1</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>1.03</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -9095,7 +9099,7 @@
       <c r="O135" s="2" t="n"/>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q135" s="2" t="n"/>
@@ -9104,11 +9108,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S135" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
-        </is>
-      </c>
+      <c r="S135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1) [T4-5]</t>
+          <t>T-2 (viga 2) [T1-2]</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+          <t>En el plano son vigas separadas (cajones distintos); entre los dos cajones no hay trabe en el modelo (hueco del plano): cada cajón se arma aparte.</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 1) [T4-5]</t>
+          <t>T-2 (viga 2) [T1-2]</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2) [T1-2]</t>
+          <t>T-2 (viga 2) [T4-6]</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2) [T1-2]</t>
+          <t>T-2 (viga 2) [T4-6]</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1.4</v>
+        <v>0.54</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
       <c r="O139" s="2" t="n"/>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q139" s="2" t="n"/>
@@ -9370,24 +9370,24 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2) [T3]</t>
+          <t>T-2 (viga 2) [T4-6]</t>
         </is>
       </c>
       <c r="C140" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>4 (viga)</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
         <v>1</v>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>1.03</v>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
       <c r="O140" s="2" t="n"/>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q140" s="2" t="n"/>
@@ -9421,11 +9421,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S140" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
-        </is>
-      </c>
+      <c r="S140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9435,7 +9431,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2) [T4-6]</t>
+          <t>T-2 (viga 3)</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -9452,7 +9448,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.72</v>
+        <v>1.42</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -9486,11 +9482,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S141" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
-        </is>
-      </c>
+      <c r="S141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9500,7 +9492,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2) [T4-6]</t>
+          <t>T-2 (viga 3)</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -9517,7 +9509,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.54</v>
+        <v>0.99</v>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
@@ -9542,7 +9534,7 @@
       <c r="O142" s="2" t="n"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q142" s="2" t="n"/>
@@ -9561,24 +9553,24 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 2) [T4-6]</t>
+          <t>T-2 (viga 4)</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -9603,7 +9595,7 @@
       <c r="O143" s="2" t="n"/>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q143" s="2" t="n"/>
@@ -9622,24 +9614,24 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 3)</t>
+          <t>T-2 (viga 4)</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1.42</v>
+        <v>0.99</v>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
@@ -9664,7 +9656,7 @@
       <c r="O144" s="2" t="n"/>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q144" s="2" t="n"/>
@@ -9683,24 +9675,24 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 3)</t>
+          <t>T-2' (viga 1) [T1-2]</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F145" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -9725,7 +9717,7 @@
       <c r="O145" s="2" t="n"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q145" s="2" t="n"/>
@@ -9734,7 +9726,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S145" s="2" t="n"/>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos); entre los dos cajones no hay trabe en el modelo (hueco del plano): cada cajón se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9744,24 +9740,24 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 4)</t>
+          <t>T-2' (viga 1) [T1-2]</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
@@ -9786,7 +9782,7 @@
       <c r="O146" s="2" t="n"/>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q146" s="2" t="n"/>
@@ -9805,24 +9801,24 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>T-2 (viga 4)</t>
+          <t>T-2' (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F147" t="n">
-        <v>0.99</v>
+        <v>1.4</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -9847,7 +9843,7 @@
       <c r="O147" s="2" t="n"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q147" s="2" t="n"/>
@@ -9856,7 +9852,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S147" s="2" t="n"/>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9866,24 +9866,24 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1) [T1-2]</t>
+          <t>T-2' (viga 1) [T4-5]</t>
         </is>
       </c>
       <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
         <v>1</v>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>1.01</v>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
       <c r="O148" s="2" t="n"/>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q148" s="2" t="n"/>
@@ -9917,11 +9917,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S148" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado. | 2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9931,38 +9927,38 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1) [T1-2]</t>
+          <t>T-2' (viga 2)</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F149" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>30x80</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="J149" s="2" t="n"/>
@@ -9973,7 +9969,7 @@
       <c r="O149" s="2" t="n"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q149" s="2" t="n"/>
@@ -9992,49 +9988,53 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1) [T3]</t>
+          <t>T-2' (viga 2)</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>30x80</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="J150" s="2" t="n"/>
-      <c r="K150" s="2" t="n"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>3#8 265/120</t>
+        </is>
+      </c>
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="2" t="n"/>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q150" s="2" t="n"/>
@@ -10043,11 +10043,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S150" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
-        </is>
-      </c>
+      <c r="S150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -10057,38 +10053,38 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1) [T4-5]</t>
+          <t>T-2' (viga 2)</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1.4</v>
+        <v>3.41</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>30x80</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="J151" s="2" t="n"/>
@@ -10096,10 +10092,14 @@
       <c r="L151" s="2" t="n"/>
       <c r="M151" s="2" t="n"/>
       <c r="N151" s="2" t="n"/>
-      <c r="O151" s="2" t="n"/>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>3#8 50</t>
+        </is>
+      </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q151" s="2" t="n"/>
@@ -10108,11 +10108,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S151" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
-        </is>
-      </c>
+      <c r="S151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -10122,28 +10118,28 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 1) [T4-5]</t>
+          <t>T-3 (viga 1)</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2.56</v>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -10164,7 +10160,7 @@
       <c r="O152" s="2" t="n"/>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q152" s="2" t="n"/>
@@ -10173,7 +10169,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S152" s="2" t="n"/>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 2)</t>
+          <t>T-3 (viga 2)</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -10200,21 +10200,21 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1.4</v>
+        <v>2.56</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>30x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J153" s="2" t="n"/>
@@ -10225,7 +10225,7 @@
       <c r="O153" s="2" t="n"/>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q153" s="2" t="n"/>
@@ -10244,53 +10244,49 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 2)</t>
+          <t>T-4 (viga 1)</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F154" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>30x80</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J154" s="2" t="n"/>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>3#8 265/120</t>
-        </is>
-      </c>
+      <c r="K154" s="2" t="n"/>
       <c r="L154" s="2" t="n"/>
       <c r="M154" s="2" t="n"/>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="2" t="n"/>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q154" s="2" t="n"/>
@@ -10299,7 +10295,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S154" s="2" t="n"/>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -10309,38 +10309,38 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>T-2' (viga 2)</t>
+          <t>T-4 (viga 1)</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
           <t>3 (viga)</t>
         </is>
       </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>4 (viga)</t>
-        </is>
-      </c>
       <c r="F155" t="n">
-        <v>3.41</v>
+        <v>1.41</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>30x80</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J155" s="2" t="n"/>
@@ -10348,14 +10348,10 @@
       <c r="L155" s="2" t="n"/>
       <c r="M155" s="2" t="n"/>
       <c r="N155" s="2" t="n"/>
-      <c r="O155" s="2" t="inlineStr">
-        <is>
-          <t>3#8 50</t>
-        </is>
-      </c>
+      <c r="O155" s="2" t="n"/>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q155" s="2" t="n"/>
@@ -10374,7 +10370,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>T-3 (viga 1)</t>
+          <t>T-4 (viga 2)</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -10387,15 +10383,15 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>2 (muro)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2.56</v>
+        <v>1.4</v>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -10416,7 +10412,7 @@
       <c r="O156" s="2" t="n"/>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q156" s="2" t="n"/>
@@ -10425,11 +10421,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S156" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -10439,28 +10431,28 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>T-3 (viga 2)</t>
+          <t>T-4 (viga 2)</t>
         </is>
       </c>
       <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
         <v>1</v>
       </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>2.56</v>
-      </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -10481,7 +10473,7 @@
       <c r="O157" s="2" t="n"/>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q157" s="2" t="n"/>
@@ -10500,7 +10492,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>T-4 (viga 1)</t>
+          <t>T-4 (viga 3)</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -10517,7 +10509,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
@@ -10551,11 +10543,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S158" s="2" t="inlineStr">
-        <is>
-          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10565,7 +10553,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>T-4 (viga 1)</t>
+          <t>T-4 (viga 3)</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -10582,7 +10570,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -10626,7 +10614,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>T-4 (viga 2)</t>
+          <t>T-4'</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -10643,21 +10631,21 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1.4</v>
+        <v>2.56</v>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J160" s="2" t="n"/>
@@ -10687,7 +10675,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>T-4 (viga 2)</t>
+          <t>T-4'</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -10704,21 +10692,21 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>3.43</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J161" s="2" t="n"/>
@@ -10748,7 +10736,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>T-4 (viga 3)</t>
+          <t>T-5 (viga 1)</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -10765,32 +10753,44 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1.4</v>
+        <v>6.11</v>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n"/>
-      <c r="K162" s="2" t="n"/>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>1#4 190</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>1#4 190</t>
+        </is>
+      </c>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
       <c r="N162" s="2" t="n"/>
-      <c r="O162" s="2" t="n"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>2#4 80</t>
+        </is>
+      </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q162" s="2" t="n"/>
@@ -10799,7 +10799,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S162" s="2" t="n"/>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -10809,49 +10813,53 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>T-4 (viga 3)</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>1 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>1.83</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J163" s="2" t="n"/>
-      <c r="K163" s="2" t="n"/>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>3#6 400/120</t>
+        </is>
+      </c>
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="2" t="n"/>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q163" s="2" t="n"/>
@@ -10860,7 +10868,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S163" s="2" t="n"/>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: ejes 5-8 (S1+S2) y ejes 9-11 (S3, 30X80); cada parte se arma aparte. | Plano: ejes 5-8 (sup. 2#6, inf. 3#6, bastón sup. 3#6 del extremo a 120 cm pasando el muro) y ejes 9-11 (30X80, 3#12). Los tramos 5 y 6 (30x80 antes del eje 9) no vienen detallados: se supuso 3#12 @10. | secciones: T-5 Seccion 1 + T-5 Seccion 2 + T-5 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -10870,33 +10882,33 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>T-4'</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2.56</v>
+        <v>0.01</v>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -10912,7 +10924,7 @@
       <c r="O164" s="2" t="n"/>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q164" s="2" t="n"/>
@@ -10931,33 +10943,33 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>T-4'</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>3.43</v>
+        <v>1.51</v>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -10973,7 +10985,7 @@
       <c r="O165" s="2" t="n"/>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q165" s="2" t="n"/>
@@ -10992,28 +11004,28 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 1)</t>
+          <t>T-5 (viga 2) [S1, S2]</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>5 (viga)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>6.11</v>
+        <v>1.66</v>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -11023,30 +11035,18 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>1#4 190</t>
-        </is>
-      </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>1#4 190</t>
-        </is>
-      </c>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n"/>
+      <c r="K166" s="2" t="n"/>
       <c r="L166" s="2" t="n"/>
       <c r="M166" s="2" t="n"/>
       <c r="N166" s="2" t="n"/>
-      <c r="O166" s="2" t="inlineStr">
-        <is>
-          <t>2#4 80</t>
-        </is>
-      </c>
+      <c r="O166" s="2" t="n"/>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q166" s="2" t="n"/>
@@ -11055,11 +11055,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S166" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -11069,7 +11065,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2) [S1, S2]</t>
+          <t>T-5 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -11077,45 +11073,45 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>1 (muro bajo la viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1.83</v>
+        <v>6.12</v>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>30x80</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#12</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#12</t>
         </is>
       </c>
       <c r="J167" s="2" t="n"/>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>3#6 400/120</t>
-        </is>
-      </c>
+      <c r="K167" s="2" t="n"/>
       <c r="L167" s="2" t="n"/>
       <c r="M167" s="2" t="n"/>
       <c r="N167" s="2" t="n"/>
-      <c r="O167" s="2" t="n"/>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>3#12 80</t>
+        </is>
+      </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q167" s="2" t="n"/>
@@ -11126,7 +11122,7 @@
       </c>
       <c r="S167" s="2" t="inlineStr">
         <is>
-          <t>En el plano son vigas separadas: ejes 5-8 (S1+S2) y ejes 9-11 (S3, 30X80); cada parte se arma aparte. | Plano: ejes 5-8 (sup. 2#6, inf. 3#6, bastón sup. 3#6 del extremo a 120 cm pasando el muro) y ejes 9-11 (30X80, 3#12). Los tramos 5 y 6 (30x80 antes del eje 9) no vienen detallados: se supuso 3#12 @10. | secciones: T-5 Seccion 1 + T-5 Seccion 2 + T-5 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>En el plano son vigas separadas: ejes 5-8 (S1+S2) y ejes 9-11 (S3, 30X80); cada parte se arma aparte.</t>
         </is>
       </c>
     </row>
@@ -11138,38 +11134,38 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2) [S1, S2]</t>
+          <t>T-6 (viga 1) [T1]</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.01</v>
+        <v>2.56</v>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J168" s="2" t="n"/>
@@ -11180,7 +11176,7 @@
       <c r="O168" s="2" t="n"/>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q168" s="2" t="n"/>
@@ -11189,7 +11185,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S168" s="2" t="n"/>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos); entre los dos cajones no hay trabe en el modelo (hueco del plano): cada cajón se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -11199,38 +11199,38 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2) [S1, S2]</t>
+          <t>T-6 (viga 1) [T3]</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1.51</v>
+        <v>2.55</v>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J169" s="2" t="n"/>
@@ -11241,7 +11241,7 @@
       <c r="O169" s="2" t="n"/>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q169" s="2" t="n"/>
@@ -11250,7 +11250,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S169" s="2" t="n"/>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -11260,33 +11264,33 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2) [S1, S2]</t>
+          <t>T-6 (viga 2) [S2]</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1.66</v>
+        <v>8.82</v>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>30x80</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
@@ -11299,10 +11303,14 @@
       <c r="L170" s="2" t="n"/>
       <c r="M170" s="2" t="n"/>
       <c r="N170" s="2" t="n"/>
-      <c r="O170" s="2" t="n"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>2#6 130</t>
+        </is>
+      </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 11@10,5@15 @20</t>
         </is>
       </c>
       <c r="Q170" s="2" t="n"/>
@@ -11311,7 +11319,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S170" s="2" t="n"/>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: 30X80 (S2) y 15X80 (S3); cada parte se arma aparte. | Los tramos 2 y 3 (30x80 entre ejes 8 y 9) no vienen detallados: se supuso @10. | secciones: T-6 Seccion 2 + T-6 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -11321,7 +11333,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>T-5 (viga 2) [S3]</t>
+          <t>T-6 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -11338,33 +11350,33 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>6.12</v>
+        <v>2.56</v>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>30x80</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>3#12</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>3#12</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J171" s="2" t="n"/>
-      <c r="K171" s="2" t="n"/>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>2#6 90/120</t>
+        </is>
+      </c>
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="2" t="n"/>
       <c r="N171" s="2" t="n"/>
-      <c r="O171" s="2" t="inlineStr">
-        <is>
-          <t>3#12 80</t>
-        </is>
-      </c>
+      <c r="O171" s="2" t="n"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
           <t>E#3 11@10 @20 11@10</t>
@@ -11378,7 +11390,7 @@
       </c>
       <c r="S171" s="2" t="inlineStr">
         <is>
-          <t>En el plano son vigas separadas: ejes 5-8 (S1+S2) y ejes 9-11 (S3, 30X80); cada parte se arma aparte.</t>
+          <t>En el plano son vigas separadas: 30X80 (S2) y 15X80 (S3); cada parte se arma aparte.</t>
         </is>
       </c>
     </row>
@@ -11390,38 +11402,38 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 1) [T1]</t>
+          <t>T-6 (viga 2) [S3]</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2.56</v>
+        <v>3.41</v>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J172" s="2" t="n"/>
@@ -11441,11 +11453,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S172" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado. | 2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -11455,7 +11463,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 1) [T2]</t>
+          <t>T-7</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -11472,7 +11480,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1.03</v>
+        <v>3.27</v>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
@@ -11506,11 +11514,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S173" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
-        </is>
-      </c>
+      <c r="S173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -11520,7 +11524,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 1) [T3]</t>
+          <t>T-7'</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -11528,30 +11532,30 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>1 (muro)</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>2 (muro)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="J174" s="2" t="n"/>
@@ -11571,11 +11575,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S174" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo entre los dos cajones no viene en el plano: se supuso el mismo armado.</t>
-        </is>
-      </c>
+      <c r="S174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -11585,38 +11585,38 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2) [S2]</t>
+          <t>T-7'</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>8.82</v>
+        <v>2.81</v>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>30x80</t>
+          <t>15x80</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="J175" s="2" t="n"/>
@@ -11624,14 +11624,10 @@
       <c r="L175" s="2" t="n"/>
       <c r="M175" s="2" t="n"/>
       <c r="N175" s="2" t="n"/>
-      <c r="O175" s="2" t="inlineStr">
-        <is>
-          <t>2#6 130</t>
-        </is>
-      </c>
+      <c r="O175" s="2" t="n"/>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10,5@15 @20</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q175" s="2" t="n"/>
@@ -11640,11 +11636,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S175" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas: 30X80 (S2) y 15X80 (S3); cada parte se arma aparte. | Los tramos 2 y 3 (30x80 entre ejes 8 y 9) no vienen detallados: se supuso @10. | secciones: T-6 Seccion 2 + T-6 Seccion 3 (se arman juntas; los bastones pasan el cambio de sección)</t>
-        </is>
-      </c>
+      <c r="S175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -11654,24 +11646,24 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2) [S3]</t>
+          <t>T-7'</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
@@ -11680,22 +11672,26 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="J176" s="2" t="n"/>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2#6 90/120</t>
+          <t>2#8 290/350</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
-      <c r="M176" s="2" t="n"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>3#8 290/350</t>
+        </is>
+      </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="2" t="n"/>
       <c r="P176" s="2" t="inlineStr">
@@ -11709,11 +11705,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S176" s="2" t="inlineStr">
-        <is>
-          <t>En el plano son vigas separadas: 30X80 (S2) y 15X80 (S3); cada parte se arma aparte.</t>
-        </is>
-      </c>
+      <c r="S176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -11723,24 +11715,24 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>T-6 (viga 2) [S3]</t>
+          <t>T-7'</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>5 (viga)</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
@@ -11749,12 +11741,12 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>2#8</t>
         </is>
       </c>
       <c r="J177" s="2" t="n"/>
@@ -11765,7 +11757,7 @@
       <c r="O177" s="2" t="n"/>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q177" s="2" t="n"/>
@@ -11784,7 +11776,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>T-7</t>
+          <t>T-8 (viga 1)</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -11801,7 +11793,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3.27</v>
+        <v>2.52</v>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
@@ -11826,7 +11818,7 @@
       <c r="O178" s="2" t="n"/>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q178" s="2" t="n"/>
@@ -11835,7 +11827,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S178" s="2" t="n"/>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>Plano: tres claros de 15X60 con 3#4 (uno @10 y dos 11@10 @20 11@10); se asignó @10 a la viga de un tramo. Revisar si corresponde a otra. | 4 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -11845,7 +11841,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>T-7'</t>
+          <t>T-8 (viga 2)</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -11853,7 +11849,7 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>1 (muro)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
@@ -11862,21 +11858,21 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J179" s="2" t="n"/>
@@ -11887,7 +11883,7 @@
       <c r="O179" s="2" t="n"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q179" s="2" t="n"/>
@@ -11906,7 +11902,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>T-7'</t>
+          <t>T-8 (viga 2)</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -11923,21 +11919,21 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2.81</v>
+        <v>1.29</v>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J180" s="2" t="n"/>
@@ -11948,7 +11944,7 @@
       <c r="O180" s="2" t="n"/>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q180" s="2" t="n"/>
@@ -11967,57 +11963,49 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>T-7'</t>
+          <t>T-8 (viga 3)</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2.81</v>
+        <v>1.3</v>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J181" s="2" t="n"/>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>2#8 290/350</t>
-        </is>
-      </c>
+      <c r="K181" s="2" t="n"/>
       <c r="L181" s="2" t="n"/>
-      <c r="M181" s="2" t="inlineStr">
-        <is>
-          <t>3#8 290/350</t>
-        </is>
-      </c>
+      <c r="M181" s="2" t="n"/>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="2" t="n"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q181" s="2" t="n"/>
@@ -12036,38 +12024,38 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>T-7'</t>
+          <t>T-8 (viga 3)</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3.27</v>
+        <v>1.08</v>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2#8</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J182" s="2" t="n"/>
@@ -12078,7 +12066,7 @@
       <c r="O182" s="2" t="n"/>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q182" s="2" t="n"/>
@@ -12097,7 +12085,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>T-8 (viga 1)</t>
+          <t>T-8 (viga 4)</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -12114,21 +12102,21 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2.52</v>
+        <v>3.27</v>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>30x40</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>5#6</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>5#6</t>
         </is>
       </c>
       <c r="J183" s="2" t="n"/>
@@ -12139,7 +12127,7 @@
       <c r="O183" s="2" t="n"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q183" s="2" t="n"/>
@@ -12148,11 +12136,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S183" s="2" t="inlineStr">
-        <is>
-          <t>Plano: tres claros de 15X60 con 3#4 (uno @10 y dos 11@10 @20 11@10); se asignó @10 a la viga de un tramo. Revisar si corresponde a otra. | 4 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -12162,7 +12146,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>T-8 (viga 2)</t>
+          <t>T-9 (viga 1)</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -12170,16 +12154,16 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>1 (muro)</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1.12</v>
+        <v>3.38</v>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
@@ -12204,7 +12188,7 @@
       <c r="O184" s="2" t="n"/>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q184" s="2" t="n"/>
@@ -12213,7 +12197,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S184" s="2" t="n"/>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -12223,24 +12211,24 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>T-8 (viga 2)</t>
+          <t>T-9 (viga 2)</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F185" t="n">
-        <v>1.29</v>
+        <v>0.52</v>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
@@ -12265,7 +12253,7 @@
       <c r="O185" s="2" t="n"/>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q185" s="2" t="n"/>
@@ -12284,24 +12272,24 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>T-8 (viga 3)</t>
+          <t>T-9 (viga 2)</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
@@ -12326,7 +12314,7 @@
       <c r="O186" s="2" t="n"/>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q186" s="2" t="n"/>
@@ -12345,24 +12333,24 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>T-8 (viga 3)</t>
+          <t>T-9 (viga 2)</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
@@ -12387,7 +12375,7 @@
       <c r="O187" s="2" t="n"/>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q187" s="2" t="n"/>
@@ -12406,7 +12394,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>T-8 (viga 4)</t>
+          <t>T-10 (viga 1)</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -12423,21 +12411,21 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3.27</v>
+        <v>2.49</v>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>30x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>5#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>5#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J188" s="2" t="n"/>
@@ -12448,7 +12436,7 @@
       <c r="O188" s="2" t="n"/>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q188" s="2" t="n"/>
@@ -12457,7 +12445,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S188" s="2" t="n"/>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -12467,7 +12459,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>T-9 (viga 1)</t>
+          <t>T-10 (viga 2)</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -12475,16 +12467,16 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>1 (muro)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>2 (muro)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3.38</v>
+        <v>1.2</v>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
@@ -12493,12 +12485,12 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J189" s="2" t="n"/>
@@ -12509,7 +12501,7 @@
       <c r="O189" s="2" t="n"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q189" s="2" t="n"/>
@@ -12518,11 +12510,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S189" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -12532,24 +12520,24 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>T-9 (viga 2)</t>
+          <t>T-10 (viga 2)</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>0.52</v>
+        <v>0.97</v>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
@@ -12558,12 +12546,12 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J190" s="2" t="n"/>
@@ -12574,7 +12562,7 @@
       <c r="O190" s="2" t="n"/>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q190" s="2" t="n"/>
@@ -12593,24 +12581,24 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>T-9 (viga 2)</t>
+          <t>T-10 (viga 2)</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
@@ -12619,12 +12607,12 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J191" s="2" t="n"/>
@@ -12635,7 +12623,7 @@
       <c r="O191" s="2" t="n"/>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q191" s="2" t="n"/>
@@ -12654,24 +12642,24 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>T-9 (viga 2)</t>
+          <t>T-10 (viga 2)</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>5 (viga)</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>0.61</v>
+        <v>2.71</v>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
@@ -12680,12 +12668,12 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J192" s="2" t="n"/>
@@ -12696,7 +12684,7 @@
       <c r="O192" s="2" t="n"/>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q192" s="2" t="n"/>
@@ -12715,24 +12703,24 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>T-10 (viga 1)</t>
+          <t>T-10 (viga 2)</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>5 (viga)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>6 (viga)</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>2.49</v>
+        <v>1.32</v>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
@@ -12741,12 +12729,12 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J193" s="2" t="n"/>
@@ -12766,11 +12754,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S193" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -12784,20 +12768,20 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>6 (viga)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>7 (viga)</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
@@ -12845,20 +12829,20 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>7 (viga)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>8 (viga)</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
@@ -12906,20 +12890,20 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>8 (viga)</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>9 (viga)</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1.44</v>
+        <v>0.91</v>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
@@ -12967,20 +12951,20 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>9 (viga)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>10 (viga)</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2.71</v>
+        <v>0.55</v>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
@@ -13005,7 +12989,7 @@
       <c r="O197" s="2" t="n"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q197" s="2" t="n"/>
@@ -13024,38 +13008,38 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>T-10 (viga 2)</t>
+          <t>T-11 (viga 1)</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>1 (muro)</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>4#6</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>4#6</t>
         </is>
       </c>
       <c r="J198" s="2" t="n"/>
@@ -13066,7 +13050,7 @@
       <c r="O198" s="2" t="n"/>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q198" s="2" t="n"/>
@@ -13075,7 +13059,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S198" s="2" t="n"/>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos); secciones: T-11 Seccion 1 + T-11 Seccion 2 (se arman juntas; los bastones pasan el cambio de sección)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -13085,24 +13073,24 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>T-10 (viga 2)</t>
+          <t>T-11 (viga 1)</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>6 (viga)</t>
+          <t>2 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>7 (viga)</t>
+          <t>3 (muro)</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
@@ -13111,23 +13099,31 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>4#6</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>4#6</t>
         </is>
       </c>
       <c r="J199" s="2" t="n"/>
-      <c r="K199" s="2" t="n"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>2#4 200/200</t>
+        </is>
+      </c>
       <c r="L199" s="2" t="n"/>
-      <c r="M199" s="2" t="n"/>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>2#4 200/200</t>
+        </is>
+      </c>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="2" t="n"/>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q199" s="2" t="n"/>
@@ -13146,24 +13142,24 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>T-10 (viga 2)</t>
+          <t>T-11 (viga 1)</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>7 (viga)</t>
+          <t>3 (muro)</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>8 (viga)</t>
+          <t>4 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
@@ -13172,12 +13168,12 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>4#6</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>4#6</t>
         </is>
       </c>
       <c r="J200" s="2" t="n"/>
@@ -13188,7 +13184,7 @@
       <c r="O200" s="2" t="n"/>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q200" s="2" t="n"/>
@@ -13207,24 +13203,24 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>T-10 (viga 2)</t>
+          <t>T-11 (viga 2)</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>8 (viga)</t>
+          <t>1 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>9 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
@@ -13233,18 +13229,26 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J201" s="2" t="n"/>
-      <c r="K201" s="2" t="n"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>2#4 190/210</t>
+        </is>
+      </c>
       <c r="L201" s="2" t="n"/>
-      <c r="M201" s="2" t="n"/>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>2#4 190/210</t>
+        </is>
+      </c>
       <c r="N201" s="2" t="n"/>
       <c r="O201" s="2" t="n"/>
       <c r="P201" s="2" t="inlineStr">
@@ -13268,24 +13272,24 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>T-10 (viga 2)</t>
+          <t>T-11 (viga 2)</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>9 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>10 (viga)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
@@ -13294,12 +13298,12 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J202" s="2" t="n"/>
@@ -13329,7 +13333,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 1)</t>
+          <t>T-11 (viga 3)</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -13337,41 +13341,49 @@
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>1 (muro)</t>
+          <t>1 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>4#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>4#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J203" s="2" t="n"/>
-      <c r="K203" s="2" t="n"/>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>2#4 200/200</t>
+        </is>
+      </c>
       <c r="L203" s="2" t="n"/>
-      <c r="M203" s="2" t="n"/>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>2#4 200/200</t>
+        </is>
+      </c>
       <c r="N203" s="2" t="n"/>
       <c r="O203" s="2" t="n"/>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q203" s="2" t="n"/>
@@ -13382,7 +13394,7 @@
       </c>
       <c r="S203" s="2" t="inlineStr">
         <is>
-          <t>3 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos); secciones: T-11 Seccion 1 + T-11 Seccion 2 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>secciones: T-11 Seccion 2 + T-11 Seccion 1 (se arman juntas; los bastones pasan el cambio de sección)</t>
         </is>
       </c>
     </row>
@@ -13394,7 +13406,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 1)</t>
+          <t>T-11 (viga 3)</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -13402,16 +13414,16 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>3 (muro)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
@@ -13420,26 +13432,18 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>4#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>4#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J204" s="2" t="n"/>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>2#4 200/200</t>
-        </is>
-      </c>
+      <c r="K204" s="2" t="n"/>
       <c r="L204" s="2" t="n"/>
-      <c r="M204" s="2" t="inlineStr">
-        <is>
-          <t>2#4 200/200</t>
-        </is>
-      </c>
+      <c r="M204" s="2" t="n"/>
       <c r="N204" s="2" t="n"/>
       <c r="O204" s="2" t="n"/>
       <c r="P204" s="2" t="inlineStr">
@@ -13463,7 +13467,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 1)</t>
+          <t>T-11 (viga 3)</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -13471,30 +13475,30 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>3 (muro)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>4 (muro bajo la viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>0.91</v>
+        <v>1.94</v>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>4#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>4#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J205" s="2" t="n"/>
@@ -13505,7 +13509,7 @@
       <c r="O205" s="2" t="n"/>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 -</t>
         </is>
       </c>
       <c r="Q205" s="2" t="n"/>
@@ -13524,28 +13528,28 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 2)</t>
+          <t>T-11 (viga 3)</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>1 (muro bajo la viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>5 (viga)</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0.86</v>
+        <v>0.61</v>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -13559,22 +13563,14 @@
         </is>
       </c>
       <c r="J206" s="2" t="n"/>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>2#4 190/210</t>
-        </is>
-      </c>
+      <c r="K206" s="2" t="n"/>
       <c r="L206" s="2" t="n"/>
-      <c r="M206" s="2" t="inlineStr">
-        <is>
-          <t>2#4 190/210</t>
-        </is>
-      </c>
+      <c r="M206" s="2" t="n"/>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="2" t="n"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 - @20 11@10</t>
         </is>
       </c>
       <c r="Q206" s="2" t="n"/>
@@ -13593,24 +13589,24 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 2)</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>3 (muro bajo la viga)</t>
-        </is>
-      </c>
       <c r="F207" t="n">
-        <v>0.77</v>
+        <v>3.04</v>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
@@ -13619,12 +13615,12 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J207" s="2" t="n"/>
@@ -13632,10 +13628,14 @@
       <c r="L207" s="2" t="n"/>
       <c r="M207" s="2" t="n"/>
       <c r="N207" s="2" t="n"/>
-      <c r="O207" s="2" t="n"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>2#6 50</t>
+        </is>
+      </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q207" s="2" t="n"/>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 3)</t>
+          <t>T-13 (viga 1)</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -13662,16 +13662,16 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>1 (muro bajo la viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
@@ -13689,22 +13689,14 @@
         </is>
       </c>
       <c r="J208" s="2" t="n"/>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>2#4 200/200</t>
-        </is>
-      </c>
+      <c r="K208" s="2" t="n"/>
       <c r="L208" s="2" t="n"/>
-      <c r="M208" s="2" t="inlineStr">
-        <is>
-          <t>2#4 200/200</t>
-        </is>
-      </c>
+      <c r="M208" s="2" t="n"/>
       <c r="N208" s="2" t="n"/>
       <c r="O208" s="2" t="n"/>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="n"/>
@@ -13715,7 +13707,7 @@
       </c>
       <c r="S208" s="2" t="inlineStr">
         <is>
-          <t>secciones: T-11 Seccion 2 + T-11 Seccion 1 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
         </is>
       </c>
     </row>
@@ -13727,24 +13719,24 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 3)</t>
+          <t>T-13 (viga 2)</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>3 (muro bajo la viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0.98</v>
+        <v>2.79</v>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
@@ -13769,7 +13761,7 @@
       <c r="O209" s="2" t="n"/>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 @20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="n"/>
@@ -13788,38 +13780,38 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 3)</t>
+          <t>T-14</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>3 (muro bajo la viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J210" s="2" t="n"/>
@@ -13830,7 +13822,7 @@
       <c r="O210" s="2" t="n"/>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 -</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q210" s="2" t="n"/>
@@ -13849,38 +13841,38 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>T-11 (viga 3)</t>
+          <t>T-15 (viga 1)</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>0.61</v>
+        <v>1.24</v>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J211" s="2" t="n"/>
@@ -13891,7 +13883,7 @@
       <c r="O211" s="2" t="n"/>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>E#3 - @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q211" s="2" t="n"/>
@@ -13900,7 +13892,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S211" s="2" t="n"/>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -13910,24 +13906,24 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-15 (viga 1)</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>3.04</v>
+        <v>1.25</v>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
@@ -13936,12 +13932,12 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J212" s="2" t="n"/>
@@ -13949,14 +13945,10 @@
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="2" t="n"/>
       <c r="N212" s="2" t="n"/>
-      <c r="O212" s="2" t="inlineStr">
-        <is>
-          <t>2#6 50</t>
-        </is>
-      </c>
+      <c r="O212" s="2" t="n"/>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q212" s="2" t="n"/>
@@ -13975,24 +13967,24 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>T-13 (viga 1)</t>
+          <t>T-15 (viga 1)</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>2 (muro)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>2.79</v>
+        <v>1.31</v>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
@@ -14001,12 +13993,12 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J213" s="2" t="n"/>
@@ -14017,7 +14009,7 @@
       <c r="O213" s="2" t="n"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q213" s="2" t="n"/>
@@ -14026,11 +14018,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S213" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -14040,7 +14028,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>T-13 (viga 2)</t>
+          <t>T-15 (viga 2)</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -14053,11 +14041,11 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>2 (muro)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
@@ -14082,7 +14070,7 @@
       <c r="O214" s="2" t="n"/>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>E#3 @20</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q214" s="2" t="n"/>
@@ -14101,7 +14089,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>T-16 (viga 1)</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -14114,11 +14102,11 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
@@ -14127,12 +14115,12 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J215" s="2" t="n"/>
@@ -14143,7 +14131,7 @@
       <c r="O215" s="2" t="n"/>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 8@10 @20 8@10</t>
         </is>
       </c>
       <c r="Q215" s="2" t="n"/>
@@ -14152,7 +14140,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S215" s="2" t="n"/>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -14162,7 +14154,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>T-15 (viga 1)</t>
+          <t>T-16 (viga 2)</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -14175,11 +14167,11 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
@@ -14188,12 +14180,12 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J216" s="2" t="n"/>
@@ -14204,7 +14196,7 @@
       <c r="O216" s="2" t="n"/>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 8@10 @20 8@10</t>
         </is>
       </c>
       <c r="Q216" s="2" t="n"/>
@@ -14213,11 +14205,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S216" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -14227,24 +14215,24 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>T-15 (viga 1)</t>
+          <t>T-17 (viga 1)</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F217" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
@@ -14253,12 +14241,12 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J217" s="2" t="n"/>
@@ -14278,7 +14266,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S217" s="2" t="n"/>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
+          <t>4 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -14288,24 +14280,24 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>T-15 (viga 1)</t>
+          <t>T-17 (viga 2)</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
@@ -14314,12 +14306,12 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>3#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J218" s="2" t="n"/>
@@ -14349,7 +14341,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>T-15 (viga 2)</t>
+          <t>T-17 (viga 3)</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -14366,7 +14358,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>2.53</v>
+        <v>1.2</v>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
@@ -14391,7 +14383,7 @@
       <c r="O219" s="2" t="n"/>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>E#3 11@10 @20 11@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q219" s="2" t="n"/>
@@ -14410,7 +14402,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>T-16 (viga 1)</t>
+          <t>T-17 (viga 4)</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -14423,11 +14415,11 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>2 (muro)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
@@ -14452,7 +14444,7 @@
       <c r="O220" s="2" t="n"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>E#3 8@10 @20 8@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q220" s="2" t="n"/>
@@ -14461,11 +14453,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S220" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -14475,7 +14463,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>T-16 (viga 2)</t>
+          <t>T-17'</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -14488,11 +14476,11 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>2 (muro)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
@@ -14501,23 +14489,35 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
-        </is>
-      </c>
-      <c r="J221" s="2" t="n"/>
-      <c r="K221" s="2" t="n"/>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>1#6 100</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>1#6 100</t>
+        </is>
+      </c>
       <c r="L221" s="2" t="n"/>
       <c r="M221" s="2" t="n"/>
       <c r="N221" s="2" t="n"/>
-      <c r="O221" s="2" t="n"/>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>2#6 50</t>
+        </is>
+      </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>E#3 8@10 @20 8@10</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q221" s="2" t="n"/>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>T-17 (viga 1)</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
@@ -14562,12 +14562,12 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J222" s="2" t="n"/>
@@ -14578,7 +14578,7 @@
       <c r="O222" s="2" t="n"/>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 @15</t>
         </is>
       </c>
       <c r="Q222" s="2" t="n"/>
@@ -14587,11 +14587,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S222" s="2" t="inlineStr">
-        <is>
-          <t>4 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -14601,24 +14597,24 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>T-17 (viga 2)</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1.2</v>
+        <v>0.91</v>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
@@ -14627,12 +14623,12 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J223" s="2" t="n"/>
@@ -14643,7 +14639,7 @@
       <c r="O223" s="2" t="n"/>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 @15</t>
         </is>
       </c>
       <c r="Q223" s="2" t="n"/>
@@ -14662,24 +14658,24 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>T-17 (viga 3)</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1.2</v>
+        <v>0.52</v>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
@@ -14688,12 +14684,12 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J224" s="2" t="n"/>
@@ -14704,7 +14700,7 @@
       <c r="O224" s="2" t="n"/>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 @15</t>
         </is>
       </c>
       <c r="Q224" s="2" t="n"/>
@@ -14723,7 +14719,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>T-17 (viga 4)</t>
+          <t>T-18' (viga 1)</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -14740,7 +14736,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
@@ -14749,15 +14745,19 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
-        </is>
-      </c>
-      <c r="J225" s="2" t="n"/>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>2#6 100</t>
+        </is>
+      </c>
       <c r="K225" s="2" t="n"/>
       <c r="L225" s="2" t="n"/>
       <c r="M225" s="2" t="n"/>
@@ -14774,7 +14774,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S225" s="2" t="n"/>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -14784,24 +14788,24 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>T-17'</t>
+          <t>T-18' (viga 1)</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3.04</v>
+        <v>0.92</v>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
@@ -14818,24 +14822,16 @@
           <t>2#6</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr">
-        <is>
-          <t>1#6 100</t>
-        </is>
-      </c>
+      <c r="J226" s="2" t="n"/>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>1#6 100</t>
+          <t>2#6 100</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
       <c r="M226" s="2" t="n"/>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="2" t="inlineStr">
-        <is>
-          <t>2#6 50</t>
-        </is>
-      </c>
+      <c r="O226" s="2" t="n"/>
       <c r="P226" s="2" t="inlineStr">
         <is>
           <t>E#3 @10</t>
@@ -14857,7 +14853,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-18' (viga 2)</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -14874,7 +14870,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>1.08</v>
+        <v>1.98</v>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
@@ -14891,7 +14887,11 @@
           <t>2#6</t>
         </is>
       </c>
-      <c r="J227" s="2" t="n"/>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>2#6 100</t>
+        </is>
+      </c>
       <c r="K227" s="2" t="n"/>
       <c r="L227" s="2" t="n"/>
       <c r="M227" s="2" t="n"/>
@@ -14899,7 +14899,7 @@
       <c r="O227" s="2" t="n"/>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>E#3 @15</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q227" s="2" t="n"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-18' (viga 2)</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
@@ -14953,14 +14953,18 @@
         </is>
       </c>
       <c r="J228" s="2" t="n"/>
-      <c r="K228" s="2" t="n"/>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>2#6 100</t>
+        </is>
+      </c>
       <c r="L228" s="2" t="n"/>
       <c r="M228" s="2" t="n"/>
       <c r="N228" s="2" t="n"/>
       <c r="O228" s="2" t="n"/>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>E#3 @15</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q228" s="2" t="n"/>
@@ -14979,38 +14983,38 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-19 (viga 1)</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>1 (muro)</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>extremo libre</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>0.52</v>
+        <v>1.41</v>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J229" s="2" t="n"/>
@@ -15021,7 +15025,7 @@
       <c r="O229" s="2" t="n"/>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>E#3 @15</t>
+          <t>E#3 @10</t>
         </is>
       </c>
       <c r="Q229" s="2" t="n"/>
@@ -15030,7 +15034,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S229" s="2" t="n"/>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -15040,7 +15048,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>T-18' (viga 1)</t>
+          <t>T-19 (viga 2)</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -15048,37 +15056,33 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>1 (muro)</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>extremo libre</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
-        </is>
-      </c>
-      <c r="J230" s="2" t="inlineStr">
-        <is>
-          <t>2#6 100</t>
-        </is>
-      </c>
+          <t>3#4</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="n"/>
       <c r="K230" s="2" t="n"/>
       <c r="L230" s="2" t="n"/>
       <c r="M230" s="2" t="n"/>
@@ -15095,11 +15099,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S230" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -15109,24 +15109,24 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>T-18' (viga 1)</t>
+          <t>T-20 (viga 1)</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>3 (viga)</t>
-        </is>
-      </c>
       <c r="F231" t="n">
-        <v>0.92</v>
+        <v>1.24</v>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
@@ -15144,11 +15144,7 @@
         </is>
       </c>
       <c r="J231" s="2" t="n"/>
-      <c r="K231" s="2" t="inlineStr">
-        <is>
-          <t>2#6 100</t>
-        </is>
-      </c>
+      <c r="K231" s="2" t="n"/>
       <c r="L231" s="2" t="n"/>
       <c r="M231" s="2" t="n"/>
       <c r="N231" s="2" t="n"/>
@@ -15164,7 +15160,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S231" s="2" t="n"/>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>Plano: el claro de 15X60 más largo (1.31, vigas 2 y 5) lleva 3#6 con bastón sup. 2#6 al extremo; el de 1.24 (vigas 1 y 4) 2#6. | 6 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>T-18' (viga 2)</t>
+          <t>T-20 (viga 2)</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -15191,7 +15191,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>1.98</v>
+        <v>1.31</v>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
@@ -15200,20 +15200,20 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
-        </is>
-      </c>
-      <c r="J232" s="2" t="inlineStr">
-        <is>
-          <t>2#6 100</t>
-        </is>
-      </c>
-      <c r="K232" s="2" t="n"/>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="n"/>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>2#6 50</t>
+        </is>
+      </c>
       <c r="L232" s="2" t="n"/>
       <c r="M232" s="2" t="n"/>
       <c r="N232" s="2" t="n"/>
@@ -15239,46 +15239,42 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>T-18' (viga 2)</t>
+          <t>T-20 (viga 3)</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>1 (muro)</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>extremo libre</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0.92</v>
+        <v>1.41</v>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J233" s="2" t="n"/>
-      <c r="K233" s="2" t="inlineStr">
-        <is>
-          <t>2#6 100</t>
-        </is>
-      </c>
+      <c r="K233" s="2" t="n"/>
       <c r="L233" s="2" t="n"/>
       <c r="M233" s="2" t="n"/>
       <c r="N233" s="2" t="n"/>
@@ -15304,7 +15300,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>T-19 (viga 1)</t>
+          <t>T-20 (viga 4)</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -15312,30 +15308,30 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>1 (muro)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>extremo libre</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J234" s="2" t="n"/>
@@ -15355,11 +15351,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S234" s="2" t="inlineStr">
-        <is>
-          <t>2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
+      <c r="S234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -15369,7 +15361,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>T-19 (viga 2)</t>
+          <t>T-20 (viga 5)</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -15377,34 +15369,38 @@
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>1 (muro)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>extremo libre</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>15x40</t>
+          <t>15x60</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>3#4</t>
+          <t>3#6</t>
         </is>
       </c>
       <c r="J235" s="2" t="n"/>
-      <c r="K235" s="2" t="n"/>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>2#6 50</t>
+        </is>
+      </c>
       <c r="L235" s="2" t="n"/>
       <c r="M235" s="2" t="n"/>
       <c r="N235" s="2" t="n"/>
@@ -15430,7 +15426,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>T-20 (viga 1)</t>
+          <t>T-20 (viga 6)</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -15438,30 +15434,30 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>1 (viga)</t>
+          <t>1 (muro)</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>extremo libre</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>15x60</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2#6</t>
+          <t>3#4</t>
         </is>
       </c>
       <c r="J236" s="2" t="n"/>
@@ -15481,324 +15477,7 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S236" s="2" t="inlineStr">
-        <is>
-          <t>Plano: el claro de 15X60 más largo (1.31, vigas 2 y 5) lleva 3#6 con bastón sup. 2#6 al extremo; el de 1.24 (vigas 1 y 4) 2#6. | 6 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>Nivel Roof Garden</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>T-20 (viga 2)</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
-        <v>1</v>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="F237" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>15x60</t>
-        </is>
-      </c>
-      <c r="H237" s="2" t="inlineStr">
-        <is>
-          <t>3#6</t>
-        </is>
-      </c>
-      <c r="I237" s="2" t="inlineStr">
-        <is>
-          <t>3#6</t>
-        </is>
-      </c>
-      <c r="J237" s="2" t="n"/>
-      <c r="K237" s="2" t="inlineStr">
-        <is>
-          <t>2#6 50</t>
-        </is>
-      </c>
-      <c r="L237" s="2" t="n"/>
-      <c r="M237" s="2" t="n"/>
-      <c r="N237" s="2" t="n"/>
-      <c r="O237" s="2" t="n"/>
-      <c r="P237" s="2" t="inlineStr">
-        <is>
-          <t>E#3 @10</t>
-        </is>
-      </c>
-      <c r="Q237" s="2" t="n"/>
-      <c r="R237" s="2" t="inlineStr">
-        <is>
-          <t>#3@30</t>
-        </is>
-      </c>
-      <c r="S237" s="2" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>Nivel Roof Garden</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>T-20 (viga 3)</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>1</v>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>1 (muro)</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>extremo libre</t>
-        </is>
-      </c>
-      <c r="F238" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>15x40</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="inlineStr">
-        <is>
-          <t>3#4</t>
-        </is>
-      </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>3#4</t>
-        </is>
-      </c>
-      <c r="J238" s="2" t="n"/>
-      <c r="K238" s="2" t="n"/>
-      <c r="L238" s="2" t="n"/>
-      <c r="M238" s="2" t="n"/>
-      <c r="N238" s="2" t="n"/>
-      <c r="O238" s="2" t="n"/>
-      <c r="P238" s="2" t="inlineStr">
-        <is>
-          <t>E#3 @10</t>
-        </is>
-      </c>
-      <c r="Q238" s="2" t="n"/>
-      <c r="R238" s="2" t="inlineStr">
-        <is>
-          <t>#3@30</t>
-        </is>
-      </c>
-      <c r="S238" s="2" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>Nivel Roof Garden</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>T-20 (viga 4)</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
-        <v>1</v>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="F239" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>15x60</t>
-        </is>
-      </c>
-      <c r="H239" s="2" t="inlineStr">
-        <is>
-          <t>2#6</t>
-        </is>
-      </c>
-      <c r="I239" s="2" t="inlineStr">
-        <is>
-          <t>2#6</t>
-        </is>
-      </c>
-      <c r="J239" s="2" t="n"/>
-      <c r="K239" s="2" t="n"/>
-      <c r="L239" s="2" t="n"/>
-      <c r="M239" s="2" t="n"/>
-      <c r="N239" s="2" t="n"/>
-      <c r="O239" s="2" t="n"/>
-      <c r="P239" s="2" t="inlineStr">
-        <is>
-          <t>E#3 @10</t>
-        </is>
-      </c>
-      <c r="Q239" s="2" t="n"/>
-      <c r="R239" s="2" t="inlineStr">
-        <is>
-          <t>#3@30</t>
-        </is>
-      </c>
-      <c r="S239" s="2" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>Nivel Roof Garden</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>T-20 (viga 5)</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
-        <v>1</v>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>1 (viga)</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>2 (viga)</t>
-        </is>
-      </c>
-      <c r="F240" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>15x60</t>
-        </is>
-      </c>
-      <c r="H240" s="2" t="inlineStr">
-        <is>
-          <t>3#6</t>
-        </is>
-      </c>
-      <c r="I240" s="2" t="inlineStr">
-        <is>
-          <t>3#6</t>
-        </is>
-      </c>
-      <c r="J240" s="2" t="n"/>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>2#6 50</t>
-        </is>
-      </c>
-      <c r="L240" s="2" t="n"/>
-      <c r="M240" s="2" t="n"/>
-      <c r="N240" s="2" t="n"/>
-      <c r="O240" s="2" t="n"/>
-      <c r="P240" s="2" t="inlineStr">
-        <is>
-          <t>E#3 @10</t>
-        </is>
-      </c>
-      <c r="Q240" s="2" t="n"/>
-      <c r="R240" s="2" t="inlineStr">
-        <is>
-          <t>#3@30</t>
-        </is>
-      </c>
-      <c r="S240" s="2" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>Nivel Roof Garden</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>T-20 (viga 6)</t>
-        </is>
-      </c>
-      <c r="C241" t="n">
-        <v>1</v>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>1 (muro)</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>extremo libre</t>
-        </is>
-      </c>
-      <c r="F241" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>15x40</t>
-        </is>
-      </c>
-      <c r="H241" s="2" t="inlineStr">
-        <is>
-          <t>3#4</t>
-        </is>
-      </c>
-      <c r="I241" s="2" t="inlineStr">
-        <is>
-          <t>3#4</t>
-        </is>
-      </c>
-      <c r="J241" s="2" t="n"/>
-      <c r="K241" s="2" t="n"/>
-      <c r="L241" s="2" t="n"/>
-      <c r="M241" s="2" t="n"/>
-      <c r="N241" s="2" t="n"/>
-      <c r="O241" s="2" t="n"/>
-      <c r="P241" s="2" t="inlineStr">
-        <is>
-          <t>E#3 @10</t>
-        </is>
-      </c>
-      <c r="Q241" s="2" t="n"/>
-      <c r="R241" s="2" t="inlineStr">
-        <is>
-          <t>#3@30</t>
-        </is>
-      </c>
-      <c r="S241" s="2" t="n"/>
+      <c r="S236" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S247"/>
